--- a/e2e/fixtures/new-format/error-147-kids.xlsx
+++ b/e2e/fixtures/new-format/error-147-kids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darren/Projects/NY-Sheriff-Summer-Camp-Scheduler/e2e/fixtures/new-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB1652C-A4C1-6E4C-87C7-E38BA7A5CEE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C69B8B1-1DAB-9B4C-8C5B-A03C3C4B33B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="44800" windowHeight="25200" firstSheet="1" activeTab="1" xr2:uid="{B75E9CFD-F73C-4E0E-B330-6F712BC21BE5}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6522" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6523" uniqueCount="1354">
   <si>
     <t>Otsego</t>
   </si>
@@ -10250,7 +10250,9 @@
       <c r="AT28" s="26" t="s">
         <v>257</v>
       </c>
-      <c r="AU28" s="26"/>
+      <c r="AU28" s="26" t="s">
+        <v>148</v>
+      </c>
       <c r="AV28" s="26" t="s">
         <v>149</v>
       </c>

--- a/e2e/fixtures/new-format/error-147-kids.xlsx
+++ b/e2e/fixtures/new-format/error-147-kids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darren/Projects/NY-Sheriff-Summer-Camp-Scheduler/e2e/fixtures/new-format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18F3714-7227-FB4D-B2F9-927952155E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F474CB47-F46E-7B47-89BC-34AE52311666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="44800" windowHeight="25200" firstSheet="1" activeTab="1" xr2:uid="{B75E9CFD-F73C-4E0E-B330-6F712BC21BE5}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2433" uniqueCount="415">
   <si>
     <t>Otsego</t>
   </si>
@@ -1286,6 +1286,9 @@
   </si>
   <si>
     <t>Brave</t>
+  </si>
+  <si>
+    <t>Ted</t>
   </si>
 </sst>
 </file>
@@ -10370,7 +10373,7 @@
         <v>411</v>
       </c>
       <c r="F148" s="23" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G148" s="24" t="s">
         <v>145</v>
